--- a/data/trans_orig/IMC_inf_MED_R3-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R3-Dificultad-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>64577</v>
+        <v>74256</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>54029</v>
+        <v>62525</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>75321</v>
+        <v>85917</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.3715099916155997</v>
+        <v>0.3487821965129894</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3108318907348019</v>
+        <v>0.2936845192925873</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.4333214585354222</v>
+        <v>0.4035561939028736</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>42025</v>
+        <v>48079</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>33681</v>
+        <v>38494</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>51651</v>
+        <v>58298</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2528496606220801</v>
+        <v>0.2398319077091733</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2026488167704199</v>
+        <v>0.1920192784884396</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3107688777098289</v>
+        <v>0.2908054680388175</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>106601</v>
+        <v>122335</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>94060</v>
+        <v>108626</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>120695</v>
+        <v>138379</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.3135090558633018</v>
+        <v>0.2959452012047746</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.2766265256807106</v>
+        <v>0.2627811958386003</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3549583495059646</v>
+        <v>0.3347572530385722</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>109245</v>
+        <v>138644</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>98501</v>
+        <v>126983</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>119793</v>
+        <v>150375</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.6284900083844004</v>
+        <v>0.6512178034870106</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.5666785414645782</v>
+        <v>0.5964438060971263</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6891681092651981</v>
+        <v>0.7063154807074127</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>124179</v>
+        <v>152391</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>114553</v>
+        <v>142172</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>132523</v>
+        <v>161976</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.74715033937792</v>
+        <v>0.7601680922908266</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6892311222901714</v>
+        <v>0.7091945319611825</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.7973511832295801</v>
+        <v>0.8079807215115606</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>339</v>
+        <v>421</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>233424</v>
+        <v>291035</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>219330</v>
+        <v>274991</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>245965</v>
+        <v>304744</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.6864909441366982</v>
+        <v>0.7040547987952255</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6450416504940354</v>
+        <v>0.6652427469614279</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.7233734743192894</v>
+        <v>0.7372188041613996</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>492</v>
+        <v>594</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>40199</v>
+        <v>42220</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>31712</v>
+        <v>33729</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>50195</v>
+        <v>52937</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2479311857774363</v>
+        <v>0.2313865619339153</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1955857012463638</v>
+        <v>0.1848527468663285</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3095830636024574</v>
+        <v>0.2901249458700585</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>35174</v>
+        <v>39626</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>26738</v>
+        <v>31364</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>44812</v>
+        <v>49049</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.228772525295371</v>
+        <v>0.2208141062017267</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1739080224826122</v>
+        <v>0.1747715864610003</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2914629827751415</v>
+        <v>0.2733232165887944</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>75373</v>
+        <v>81846</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>63200</v>
+        <v>69334</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>87798</v>
+        <v>94187</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2386062833964921</v>
+        <v>0.2261442842352866</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2000690759740784</v>
+        <v>0.1915738761654472</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2779380188084404</v>
+        <v>0.2602440763573992</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>121940</v>
+        <v>140244</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>111944</v>
+        <v>129527</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>130427</v>
+        <v>148735</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7520688142225637</v>
+        <v>0.7686134380660846</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.690416936397543</v>
+        <v>0.7098750541299415</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.8044142987536366</v>
+        <v>0.8151472531336714</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>118575</v>
+        <v>139829</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>108937</v>
+        <v>130406</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>127011</v>
+        <v>148091</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7712274747046289</v>
+        <v>0.7791858937982733</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7085370172248585</v>
+        <v>0.7266767834112057</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8260919775173878</v>
+        <v>0.8252284135389996</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>240516</v>
+        <v>280072</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>228091</v>
+        <v>267731</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>252689</v>
+        <v>292584</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7613937166035079</v>
+        <v>0.7738557157647133</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7220619811915595</v>
+        <v>0.7397559236426008</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7999309240259216</v>
+        <v>0.8084261238345528</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>450</v>
+        <v>517</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>19195</v>
+        <v>19847</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>13650</v>
+        <v>13733</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>26704</v>
+        <v>27694</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1797075839494679</v>
+        <v>0.1465382090390698</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.12779466373227</v>
+        <v>0.1013971024189112</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.250003642842562</v>
+        <v>0.2044777172060235</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>18851</v>
+        <v>21497</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>12779</v>
+        <v>15566</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>26207</v>
+        <v>28819</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1751443786092909</v>
+        <v>0.1621950863079638</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1187223321655923</v>
+        <v>0.1174499587749575</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2434869196235969</v>
+        <v>0.2174436214053813</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>38047</v>
+        <v>41343</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>29040</v>
+        <v>32407</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>47526</v>
+        <v>51691</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1774172711652496</v>
+        <v>0.1542818570681252</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1354176821115135</v>
+        <v>0.1209325252602549</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2216195735895155</v>
+        <v>0.1928954306823597</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>87620</v>
+        <v>115590</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>80111</v>
+        <v>107743</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>93165</v>
+        <v>121704</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8202924160505322</v>
+        <v>0.8534617909609302</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.7499963571574372</v>
+        <v>0.7955222827939765</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8722053362677299</v>
+        <v>0.8986028975810885</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>88783</v>
+        <v>111038</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>81427</v>
+        <v>103716</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>94855</v>
+        <v>116969</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8248556213907091</v>
+        <v>0.8378049136920362</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7565130803764032</v>
+        <v>0.7825563785946187</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8812776678344078</v>
+        <v>0.8825500412250425</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>176402</v>
+        <v>226629</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>166923</v>
+        <v>216281</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>185409</v>
+        <v>235565</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8225827288347504</v>
+        <v>0.8457181429318748</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7783804264104847</v>
+        <v>0.8071045693176403</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8645823178884866</v>
+        <v>0.8790674747397452</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>17518</v>
+        <v>20071</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>11712</v>
+        <v>14779</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>23644</v>
+        <v>27717</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2704028371000486</v>
+        <v>0.2615199518274802</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.180775080313934</v>
+        <v>0.1925742258358211</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3649530238787019</v>
+        <v>0.361149944149911</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>10612</v>
+        <v>13589</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>6130</v>
+        <v>8746</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>16359</v>
+        <v>19906</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1783997243047349</v>
+        <v>0.2023087504741471</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1030508989744468</v>
+        <v>0.1302045794931488</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2750254176551273</v>
+        <v>0.2963545446202499</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>28130</v>
+        <v>33660</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>20547</v>
+        <v>25017</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>36799</v>
+        <v>42742</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2263646630862259</v>
+        <v>0.2338849702836059</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1653432101676799</v>
+        <v>0.1738333853129845</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2961232474689807</v>
+        <v>0.2969922102135011</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>47268</v>
+        <v>56676</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>41142</v>
+        <v>49030</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>53074</v>
+        <v>61968</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7295971628999514</v>
+        <v>0.7384800481725198</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6350469761212976</v>
+        <v>0.6388500558500907</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8192249196860655</v>
+        <v>0.8074257741641792</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>48870</v>
+        <v>53579</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>43123</v>
+        <v>47262</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>53352</v>
+        <v>58422</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8216002756952651</v>
+        <v>0.7976912495258529</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7249745823448727</v>
+        <v>0.7036454553797511</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8969491010255523</v>
+        <v>0.8697954205068518</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>96139</v>
+        <v>110255</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>87470</v>
+        <v>101173</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>103722</v>
+        <v>118898</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7736353369137741</v>
+        <v>0.7661150297163941</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7038767525310191</v>
+        <v>0.7030077897864989</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8346567898323201</v>
+        <v>0.8261666146870154</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>141490</v>
+        <v>156393</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>126180</v>
+        <v>140307</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>160414</v>
+        <v>175891</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.278763295473694</v>
+        <v>0.2574167342740283</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2486008816543207</v>
+        <v>0.2309402517942438</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3160481245473407</v>
+        <v>0.2895101932324498</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>106661</v>
+        <v>122790</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>92386</v>
+        <v>105807</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>122660</v>
+        <v>138713</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2189858616577576</v>
+        <v>0.2118436219599846</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1896765868961637</v>
+        <v>0.1825433812769407</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2518321382999636</v>
+        <v>0.2393150628306941</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>248151</v>
+        <v>279183</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>226765</v>
+        <v>257475</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>271289</v>
+        <v>303277</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.249490398640264</v>
+        <v>0.235166099954575</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.2279893513555058</v>
+        <v>0.2168801083385214</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2727535264293153</v>
+        <v>0.2554608400510358</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>529</v>
+        <v>650</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>366072</v>
+        <v>451155</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>347148</v>
+        <v>431657</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>381382</v>
+        <v>467241</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7212367045263061</v>
+        <v>0.7425832657259717</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.683951875452659</v>
+        <v>0.7104898067675502</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.7513991183456791</v>
+        <v>0.7690597482057565</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>544</v>
+        <v>655</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>380408</v>
+        <v>456837</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>364409</v>
+        <v>440914</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>394683</v>
+        <v>473820</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7810141383422424</v>
+        <v>0.7881563780400154</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7481678617000362</v>
+        <v>0.7606849371693059</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8103234131038363</v>
+        <v>0.8174566187230593</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1073</v>
+        <v>1305</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>746480</v>
+        <v>907992</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>723342</v>
+        <v>883898</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>767866</v>
+        <v>929700</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.750509601359736</v>
+        <v>0.7648339000454251</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.7272464735706848</v>
+        <v>0.7445391599489642</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.7720106486444943</v>
+        <v>0.7831198916614788</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>729</v>
+        <v>869</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>698</v>
+        <v>830</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1427</v>
+        <v>1699</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>44957</v>
+        <v>54271</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>35694</v>
+        <v>44905</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>54945</v>
+        <v>65864</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.226348263126446</v>
+        <v>0.2203131186823581</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1797149910590308</v>
+        <v>0.1822903063138955</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2766387773094212</v>
+        <v>0.2673759896103224</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>27271</v>
+        <v>29242</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>20085</v>
+        <v>21903</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>35422</v>
+        <v>38091</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1531424408090547</v>
+        <v>0.1347675026373799</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1127876003463152</v>
+        <v>0.1009435537025245</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1989144872160417</v>
+        <v>0.1755497689612285</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>72228</v>
+        <v>83513</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>60415</v>
+        <v>70525</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>86352</v>
+        <v>97238</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1917410100191443</v>
+        <v>0.1802502730866636</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1603814322308033</v>
+        <v>0.1522181978786718</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2292342804398897</v>
+        <v>0.2098745994398613</v>
       </c>
     </row>
     <row r="5">
@@ -2117,67 +2117,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>153660</v>
+        <v>192065</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>143672</v>
+        <v>180472</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>162923</v>
+        <v>201431</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.773651736873554</v>
+        <v>0.7796868813176419</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.7233612226905785</v>
+        <v>0.7326240103896778</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8202850089409691</v>
+        <v>0.8177096936861045</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>150808</v>
+        <v>187739</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>142657</v>
+        <v>178890</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>157994</v>
+        <v>195078</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8468575591909453</v>
+        <v>0.8652324973626201</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.8010855127839587</v>
+        <v>0.8244502310387716</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8872123996536848</v>
+        <v>0.8990564462974755</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>445</v>
+        <v>554</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>304468</v>
+        <v>379804</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>290344</v>
+        <v>366079</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>316281</v>
+        <v>392792</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.8082589899808557</v>
+        <v>0.8197497269133364</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.7707657195601102</v>
+        <v>0.79012540056014</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8396185677691966</v>
+        <v>0.8477818021213285</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2230,16 +2230,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>550</v>
+        <v>675</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2263,67 +2263,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>32199</v>
+        <v>35098</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>24327</v>
+        <v>27125</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>39984</v>
+        <v>44694</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2154345965422546</v>
+        <v>0.2065341813573121</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1627696229585819</v>
+        <v>0.1596126403791711</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2675231963896246</v>
+        <v>0.2629971386407131</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>18069</v>
+        <v>19365</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>11895</v>
+        <v>12982</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>25338</v>
+        <v>27441</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1244767918736088</v>
+        <v>0.1168514871682049</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.08194796720781918</v>
+        <v>0.07833212668107102</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.174550515522271</v>
+        <v>0.165582797347357</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>50268</v>
+        <v>54464</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>40893</v>
+        <v>44741</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>62629</v>
+        <v>66999</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1706193455928725</v>
+        <v>0.1622557720335867</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1387986842236549</v>
+        <v>0.133291375995106</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2125779966916898</v>
+        <v>0.1996000164874927</v>
       </c>
     </row>
     <row r="8">
@@ -2334,67 +2334,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>117260</v>
+        <v>134842</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>109475</v>
+        <v>125246</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>125132</v>
+        <v>142815</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7845654034577454</v>
+        <v>0.7934658186426878</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7324768036103759</v>
+        <v>0.7370028613592869</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.8372303770414183</v>
+        <v>0.8403873596208289</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>127090</v>
+        <v>146361</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>119821</v>
+        <v>138285</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>133264</v>
+        <v>152744</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8755232081263913</v>
+        <v>0.8831485128317951</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.825449484477729</v>
+        <v>0.8344172026526431</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9180520327921808</v>
+        <v>0.921667873318929</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>354</v>
+        <v>410</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>244350</v>
+        <v>281202</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>231989</v>
+        <v>268667</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>253725</v>
+        <v>290925</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8293806544071275</v>
+        <v>0.8377442279664133</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7874220033083102</v>
+        <v>0.8003999835125071</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8612013157763451</v>
+        <v>0.866708624004894</v>
       </c>
     </row>
     <row r="9">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2426,16 +2426,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2480,67 +2480,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>21170</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>14808</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>29125</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1676113253013359</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1172417831671916</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.2305984876594423</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>19446</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>13418</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>26992</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.1805100778845052</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.1245520537303901</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0.2505531678528206</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K10" s="5" t="n">
-        <v>16978</v>
+        <v>18159</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>11466</v>
+        <v>12643</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>23761</v>
+        <v>24553</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1593819648990553</v>
+        <v>0.1447363260017</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1076330100381735</v>
+        <v>0.100772140106965</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2230548691564496</v>
+        <v>0.1956993796328633</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>36424</v>
+        <v>39329</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>27888</v>
+        <v>30023</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>45643</v>
+        <v>48889</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1700052463770699</v>
+        <v>0.156211909121194</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1301655420454687</v>
+        <v>0.1192499532971736</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2130334644866656</v>
+        <v>0.19418213888041</v>
       </c>
     </row>
     <row r="11">
@@ -2551,67 +2551,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>88282</v>
+        <v>105133</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>80736</v>
+        <v>97178</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>94310</v>
+        <v>111495</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8194899221154948</v>
+        <v>0.8323886746986642</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.7494468321471797</v>
+        <v>0.7694015123405576</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.87544794626961</v>
+        <v>0.8827582168328084</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>89548</v>
+        <v>107306</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>82765</v>
+        <v>100912</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>95060</v>
+        <v>112822</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8406180351009447</v>
+        <v>0.8552636739982999</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7769451308435505</v>
+        <v>0.8043006203671367</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8923669899618265</v>
+        <v>0.8992278598930348</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>177830</v>
+        <v>212438</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>168611</v>
+        <v>202878</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>186366</v>
+        <v>221744</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8299947536229301</v>
+        <v>0.843788090878806</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7869665355133356</v>
+        <v>0.80581786111959</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8698344579545314</v>
+        <v>0.8807500467028267</v>
       </c>
     </row>
     <row r="12">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2643,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2664,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>13880</v>
+        <v>15356</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>8843</v>
+        <v>10433</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>19585</v>
+        <v>22143</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2208479712333657</v>
+        <v>0.1842341898358911</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1407035948592434</v>
+        <v>0.1251684795948807</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3116174150049497</v>
+        <v>0.2656494929928589</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>4850</v>
+        <v>6652</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2270</v>
+        <v>3564</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>9312</v>
+        <v>11209</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.09477188193758977</v>
+        <v>0.1075283413528506</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.04434932033924822</v>
+        <v>0.05760967314529093</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1819408062103348</v>
+        <v>0.1811869603607239</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>18730</v>
+        <v>22009</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>12841</v>
+        <v>16022</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>25841</v>
+        <v>29661</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1642608227014273</v>
+        <v>0.1515557362239634</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1126166371997194</v>
+        <v>0.1103300888972529</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2266160340280887</v>
+        <v>0.2042474959894231</v>
       </c>
     </row>
     <row r="14">
@@ -2768,67 +2768,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>48969</v>
+        <v>67997</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>43264</v>
+        <v>61210</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>54006</v>
+        <v>72920</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7791520287666343</v>
+        <v>0.8157658101641089</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6883825849950503</v>
+        <v>0.734350507007141</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8592964051407567</v>
+        <v>0.8748315204051192</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>46330</v>
+        <v>55215</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>41868</v>
+        <v>50658</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>48910</v>
+        <v>58303</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.9052281180624102</v>
+        <v>0.8924716586471494</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8180591937896653</v>
+        <v>0.8188130396392761</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9556506796607518</v>
+        <v>0.9423903268547091</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>95298</v>
+        <v>123211</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>88187</v>
+        <v>115559</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>101187</v>
+        <v>129198</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8357391772985726</v>
+        <v>0.8484442637760367</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7733839659719112</v>
+        <v>0.7957525040105768</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8873833628002806</v>
+        <v>0.8896699111027471</v>
       </c>
     </row>
     <row r="15">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2860,16 +2860,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>110481</v>
+        <v>125896</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>95087</v>
+        <v>111567</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>126305</v>
+        <v>143450</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2130158898517304</v>
+        <v>0.2011332831560991</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.183334200837909</v>
+        <v>0.1782417633279202</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2435261704347339</v>
+        <v>0.2291786512176086</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>67169</v>
+        <v>73419</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>55472</v>
+        <v>61034</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>78858</v>
+        <v>87107</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.139661037288564</v>
+        <v>0.1287966449128325</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1153391412167246</v>
+        <v>0.107069822093697</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1639656505792875</v>
+        <v>0.1528090719662611</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>177650</v>
+        <v>199315</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>158542</v>
+        <v>178137</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>198854</v>
+        <v>221545</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1777220344532643</v>
+        <v>0.1666552561871625</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1586063096300076</v>
+        <v>0.1489476781098522</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1989343369041466</v>
+        <v>0.1852427454441756</v>
       </c>
     </row>
     <row r="17">
@@ -2985,67 +2985,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>578</v>
+        <v>709</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>408171</v>
+        <v>500035</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>392347</v>
+        <v>482481</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>423565</v>
+        <v>514364</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7869841101482696</v>
+        <v>0.7988667168439009</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.7564738295652659</v>
+        <v>0.7708213487823913</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8166657991620909</v>
+        <v>0.8217582366720798</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>613</v>
+        <v>739</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>413776</v>
+        <v>496620</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>402087</v>
+        <v>482932</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>425473</v>
+        <v>509005</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8603389627114361</v>
+        <v>0.8712033550871675</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8360343494207125</v>
+        <v>0.847190928033739</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8846608587832757</v>
+        <v>0.8929301779063031</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1191</v>
+        <v>1448</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>821947</v>
+        <v>996655</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>800743</v>
+        <v>974425</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>841055</v>
+        <v>1017833</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.8222779655467357</v>
+        <v>0.8333447438128375</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.8010656630958534</v>
+        <v>0.8147572545558244</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8413936903699929</v>
+        <v>0.8510523218901478</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>736</v>
+        <v>888</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>716</v>
+        <v>852</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1452</v>
+        <v>1740</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3363,67 +3363,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13956</v>
+        <v>14411</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8452</v>
+        <v>8532</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>20585</v>
+        <v>20518</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.3285458242705096</v>
+        <v>0.3185351120913787</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1989767410642577</v>
+        <v>0.1885868037019313</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.4846249638997799</v>
+        <v>0.45352400117937</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5054</v>
+        <v>5623</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2366</v>
+        <v>2601</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>9256</v>
+        <v>9796</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1627782713914452</v>
+        <v>0.1671954295334659</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.07622202617572561</v>
+        <v>0.07732859881039936</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2981346073540723</v>
+        <v>0.2912670640747617</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>19009</v>
+        <v>20034</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>12361</v>
+        <v>13045</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>25458</v>
+        <v>27585</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2585473785167386</v>
+        <v>0.2540034594548781</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1681188629109684</v>
+        <v>0.1653989847022795</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3462479810050367</v>
+        <v>0.34974586736154</v>
       </c>
     </row>
     <row r="5">
@@ -3434,67 +3434,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>28521</v>
+        <v>30830</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21892</v>
+        <v>24723</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>34025</v>
+        <v>36709</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.6714541757294904</v>
+        <v>0.6814648879086211</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.5153750361002205</v>
+        <v>0.5464759988206298</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8010232589357424</v>
+        <v>0.8114131962980683</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>25993</v>
+        <v>28008</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>21791</v>
+        <v>23835</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>28681</v>
+        <v>31030</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8372217286085548</v>
+        <v>0.832804570466534</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7018653926459277</v>
+        <v>0.7087329359252381</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.9237779738242745</v>
+        <v>0.9226714011896006</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>54515</v>
+        <v>58838</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>48066</v>
+        <v>51287</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>61163</v>
+        <v>65827</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7414526214832612</v>
+        <v>0.7459965405451217</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6537520189949636</v>
+        <v>0.6502541326384599</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8318811370890313</v>
+        <v>0.8346010152977205</v>
       </c>
     </row>
     <row r="6">
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -3526,16 +3526,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3547,16 +3547,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3586,61 +3586,61 @@
         <v>14033</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>9037</v>
+        <v>8776</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>21248</v>
+        <v>20492</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1529663283915139</v>
+        <v>0.1464550628296911</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.09850868382902699</v>
+        <v>0.09158418875940412</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2316058378167584</v>
+        <v>0.2138586431820632</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>8079</v>
+        <v>8902</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>4647</v>
+        <v>4882</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>13800</v>
+        <v>15046</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1218327174608374</v>
+        <v>0.1253740161708091</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.07007976884828894</v>
+        <v>0.06875760474576549</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2081048180598798</v>
+        <v>0.2119121644132642</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>22113</v>
+        <v>22935</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15454</v>
+        <v>17034</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>30868</v>
+        <v>31820</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1399040704921548</v>
+        <v>0.1374826404912945</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.09777397040497575</v>
+        <v>0.1021069564948177</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.1952980517774775</v>
+        <v>0.19074312536887</v>
       </c>
     </row>
     <row r="8">
@@ -3651,67 +3651,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>77709</v>
+        <v>81788</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>70494</v>
+        <v>75329</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>82705</v>
+        <v>87045</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8470336716084861</v>
+        <v>0.8535449371703088</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7683941621832416</v>
+        <v>0.7861413568179367</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.901491316170973</v>
+        <v>0.9084158112405958</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>58234</v>
+        <v>62101</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>52513</v>
+        <v>55957</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>61666</v>
+        <v>66121</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8781672825391625</v>
+        <v>0.8746259838291909</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7918951819401205</v>
+        <v>0.7880878355867355</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9299202311517112</v>
+        <v>0.9312423952542344</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>135942</v>
+        <v>143888</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>127187</v>
+        <v>135003</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>142601</v>
+        <v>149789</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8600959295078453</v>
+        <v>0.8625173595087055</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.8047019482225227</v>
+        <v>0.8092568746311303</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.9022260295950243</v>
+        <v>0.8978930435051825</v>
       </c>
     </row>
     <row r="9">
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3764,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3800,22 +3800,22 @@
         <v>31</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>21266</v>
+        <v>21265</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>14445</v>
+        <v>14978</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28580</v>
+        <v>28586</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2115551990558072</v>
+        <v>0.2003953669295598</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1437045568220927</v>
+        <v>0.1411479384176006</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.284320351305977</v>
+        <v>0.2693809472819437</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>12</v>
@@ -3824,19 +3824,19 @@
         <v>6634</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3508</v>
+        <v>3616</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>11300</v>
+        <v>11645</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.08543671930181672</v>
+        <v>0.08200028338371186</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.04518455926907329</v>
+        <v>0.04469060649296772</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1455228202992948</v>
+        <v>0.1439428298583852</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>43</v>
@@ -3845,19 +3845,19 @@
         <v>27899</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>21128</v>
+        <v>20072</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>36843</v>
+        <v>36353</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1565908485468277</v>
+        <v>0.1491791933333916</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1185845591475446</v>
+        <v>0.107323525019737</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2067903568304355</v>
+        <v>0.1943786852705083</v>
       </c>
     </row>
     <row r="11">
@@ -3868,67 +3868,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>79254</v>
+        <v>84852</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>71940</v>
+        <v>77531</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>86075</v>
+        <v>91139</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7884448009441929</v>
+        <v>0.7996046330704402</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.715679648694023</v>
+        <v>0.7306190527180563</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8562954431779074</v>
+        <v>0.8588520615823995</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>71014</v>
+        <v>74268</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>66348</v>
+        <v>69257</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>74140</v>
+        <v>77286</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.914563280698183</v>
+        <v>0.9179997166162881</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8544771797007049</v>
+        <v>0.8560571701416149</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9548154407309267</v>
+        <v>0.9553093935070324</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>150269</v>
+        <v>159121</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>141325</v>
+        <v>150667</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>157040</v>
+        <v>166948</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8434091514531721</v>
+        <v>0.8508208066666083</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.793209643169564</v>
+        <v>0.8056213147294916</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8814154408524555</v>
+        <v>0.8926764749802629</v>
       </c>
     </row>
     <row r="12">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3960,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4020,61 +4020,61 @@
         <v>9043</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>5287</v>
+        <v>5443</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>14382</v>
+        <v>14069</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.1582076267734154</v>
+        <v>0.1524266951512893</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.09250126559029952</v>
+        <v>0.0917448708649537</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2516256858376809</v>
+        <v>0.2371551377250419</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>5522</v>
+        <v>6028</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>3041</v>
+        <v>3490</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>9668</v>
+        <v>9956</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1093153439261548</v>
+        <v>0.1150205333325523</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.06020601292693627</v>
+        <v>0.06658621403104997</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1913999537584541</v>
+        <v>0.1899631752648895</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>14565</v>
+        <v>15071</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>10098</v>
+        <v>10330</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>21205</v>
+        <v>21917</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1352699426047346</v>
+        <v>0.1348814781920243</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.0937823783063792</v>
+        <v>0.09245618488355944</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.1969452918799198</v>
+        <v>0.1961562052780466</v>
       </c>
     </row>
     <row r="14">
@@ -4085,67 +4085,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>48114</v>
+        <v>50282</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>42775</v>
+        <v>45256</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>51870</v>
+        <v>53882</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.8417923732265845</v>
+        <v>0.8475733048487109</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7483743141623184</v>
+        <v>0.7628448622749581</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.9074987344097003</v>
+        <v>0.9082551291350461</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>44991</v>
+        <v>46380</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>40845</v>
+        <v>42452</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>47472</v>
+        <v>48918</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8906846560738453</v>
+        <v>0.8849794666674476</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8086000462415461</v>
+        <v>0.8100368247351102</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9397939870730638</v>
+        <v>0.9334137859689496</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>93106</v>
+        <v>96662</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>86466</v>
+        <v>89816</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>97573</v>
+        <v>101403</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8647300573952653</v>
+        <v>0.8651185218079755</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.8030547081200804</v>
+        <v>0.8038437947219532</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.906217621693621</v>
+        <v>0.9075438151164406</v>
       </c>
     </row>
     <row r="15">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4198,16 +4198,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4231,67 +4231,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>58297</v>
+        <v>58752</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>47038</v>
+        <v>46213</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>71244</v>
+        <v>70141</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1997193371470469</v>
+        <v>0.1916856024640782</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1611471622096477</v>
+        <v>0.1507759486113986</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2440745766066508</v>
+        <v>0.2288430935748162</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>25289</v>
+        <v>27187</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>17802</v>
+        <v>20121</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>33518</v>
+        <v>36129</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1121345100919822</v>
+        <v>0.1142574399832456</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.07893754140301756</v>
+        <v>0.08456391666551345</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1486245077730103</v>
+        <v>0.1518392229970069</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>83586</v>
+        <v>85939</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>69808</v>
+        <v>72325</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>98232</v>
+        <v>101212</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1615446659536019</v>
+        <v>0.1578466125912172</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1349160016619218</v>
+        <v>0.1328407682315238</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1898508594071757</v>
+        <v>0.1858984285306031</v>
       </c>
     </row>
     <row r="17">
@@ -4302,67 +4302,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>233599</v>
+        <v>247752</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>220652</v>
+        <v>236363</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>244858</v>
+        <v>260291</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.8002806628529532</v>
+        <v>0.8083143975359218</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.7559254233933498</v>
+        <v>0.7711569064251838</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8388528377903528</v>
+        <v>0.8492240513886011</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>200232</v>
+        <v>210757</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>192003</v>
+        <v>201815</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>207719</v>
+        <v>217823</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8878654899080178</v>
+        <v>0.8857425600167543</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8513754922269893</v>
+        <v>0.8481607770029932</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.9210624585969824</v>
+        <v>0.9154360833344866</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>616</v>
+        <v>651</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>433831</v>
+        <v>458509</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>419185</v>
+        <v>443236</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>447609</v>
+        <v>472123</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.838455334046398</v>
+        <v>0.8421533874087828</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.8101491405928242</v>
+        <v>0.8141015714693968</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8650839983380781</v>
+        <v>0.8671592317684761</v>
       </c>
     </row>
     <row r="18">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -4394,16 +4394,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -4415,16 +4415,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>746</v>
+        <v>785</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
